--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-observation-rauchen.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-observation-rauchen.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4965" uniqueCount="607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4965" uniqueCount="609">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T19:01:50+00:00</t>
+    <t>2026-10-30T07:50:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Unknown region code '276'</t>
+    <t>Germany</t>
   </si>
   <si>
     <t>Description</t>
@@ -872,13 +872,20 @@
 </t>
   </si>
   <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+    <t>A reference to a code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.</t>
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://snomed.info/sct"/&gt;
   &lt;code value="77176002"/&gt;
 &lt;/valueCoding&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
   </si>
   <si>
     <t>Observation.code.coding:loinc</t>
@@ -5822,13 +5829,13 @@
         <v>268</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="M35" t="s" s="2">
         <v>231</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O35" t="s" s="2">
         <v>233</v>
@@ -5841,7 +5848,7 @@
         <v>76</v>
       </c>
       <c r="S35" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="T35" t="s" s="2">
         <v>76</v>
@@ -5889,7 +5896,7 @@
         <v>75</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>76</v>
+        <v>272</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>95</v>
@@ -5897,13 +5904,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>229</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>76</v>
@@ -5925,16 +5932,16 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>230</v>
+        <v>269</v>
       </c>
       <c r="M36" t="s" s="2">
         <v>231</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O36" t="s" s="2">
         <v>233</v>
@@ -5947,7 +5954,7 @@
         <v>76</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>76</v>
@@ -5995,7 +6002,7 @@
         <v>75</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>76</v>
+        <v>272</v>
       </c>
       <c r="AJ36" t="s" s="2">
         <v>95</v>
@@ -6003,10 +6010,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6032,16 +6039,16 @@
         <v>97</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>76</v>
@@ -6090,7 +6097,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>74</v>
@@ -6107,10 +6114,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6133,19 +6140,19 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -6194,7 +6201,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>74</v>
@@ -6211,10 +6218,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6311,10 +6318,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6413,10 +6420,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6442,13 +6449,13 @@
         <v>97</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6498,7 +6505,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>74</v>
@@ -6507,7 +6514,7 @@
         <v>83</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>95</v>
@@ -6515,10 +6522,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6544,13 +6551,13 @@
         <v>124</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6579,10 +6586,10 @@
         <v>140</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>76</v>
@@ -6600,7 +6607,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -6617,10 +6624,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6646,13 +6653,13 @@
         <v>189</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6702,7 +6709,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
@@ -6719,10 +6726,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6748,13 +6755,13 @@
         <v>97</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6804,7 +6811,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>74</v>
@@ -6821,10 +6828,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6847,16 +6854,16 @@
         <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6906,7 +6913,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>74</v>
@@ -6923,14 +6930,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6949,19 +6956,19 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -7010,7 +7017,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>74</v>
@@ -7027,10 +7034,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7127,10 +7134,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7229,10 +7236,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7258,13 +7265,13 @@
         <v>97</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7314,7 +7321,7 @@
         <v>76</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>74</v>
@@ -7323,7 +7330,7 @@
         <v>83</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>95</v>
@@ -7331,10 +7338,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7360,13 +7367,13 @@
         <v>124</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7395,10 +7402,10 @@
         <v>140</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>76</v>
@@ -7416,7 +7423,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>74</v>
@@ -7433,10 +7440,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7462,13 +7469,13 @@
         <v>189</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7518,7 +7525,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>74</v>
@@ -7535,10 +7542,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7564,13 +7571,13 @@
         <v>97</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -7620,7 +7627,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>74</v>
@@ -7637,14 +7644,14 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -7663,19 +7670,19 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>76</v>
@@ -7724,7 +7731,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>74</v>
@@ -7741,10 +7748,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7770,13 +7777,13 @@
         <v>118</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7826,7 +7833,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>74</v>
@@ -7843,10 +7850,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7869,17 +7876,17 @@
         <v>84</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>76</v>
@@ -7928,7 +7935,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>74</v>
@@ -7945,10 +7952,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7974,16 +7981,16 @@
         <v>213</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>76</v>
@@ -8020,17 +8027,17 @@
         <v>76</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AC56" s="2"/>
       <c r="AD56" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>74</v>
@@ -8039,7 +8046,7 @@
         <v>83</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>95</v>
@@ -8047,13 +8054,13 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>76</v>
@@ -8075,19 +8082,19 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -8136,7 +8143,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>74</v>
@@ -8145,7 +8152,7 @@
         <v>83</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>95</v>
@@ -8153,13 +8160,13 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D58" t="s" s="2">
         <v>76</v>
@@ -8184,16 +8191,16 @@
         <v>213</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>76</v>
@@ -8222,7 +8229,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>76</v>
@@ -8240,7 +8247,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>74</v>
@@ -8249,7 +8256,7 @@
         <v>83</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>95</v>
@@ -8257,10 +8264,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8286,16 +8293,16 @@
         <v>213</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>76</v>
@@ -8323,10 +8330,10 @@
         <v>140</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>76</v>
@@ -8344,7 +8351,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>74</v>
@@ -8353,7 +8360,7 @@
         <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>95</v>
@@ -8361,14 +8368,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8390,16 +8397,16 @@
         <v>213</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>76</v>
@@ -8427,10 +8434,10 @@
         <v>140</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>76</v>
@@ -8448,7 +8455,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>74</v>
@@ -8465,10 +8472,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8491,19 +8498,19 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>76</v>
@@ -8552,7 +8559,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>74</v>
@@ -8569,10 +8576,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8598,13 +8605,13 @@
         <v>213</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8633,10 +8640,10 @@
         <v>148</v>
       </c>
       <c r="Y62" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Z62" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>76</v>
@@ -8654,7 +8661,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>74</v>
@@ -8671,10 +8678,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8700,16 +8707,16 @@
         <v>213</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>76</v>
@@ -8737,10 +8744,10 @@
         <v>148</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>76</v>
@@ -8758,7 +8765,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>74</v>
@@ -8775,10 +8782,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8801,16 +8808,16 @@
         <v>76</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8860,7 +8867,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>74</v>
@@ -8877,10 +8884,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8903,16 +8910,16 @@
         <v>76</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -8962,7 +8969,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>74</v>
@@ -8979,10 +8986,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9005,19 +9012,19 @@
         <v>76</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>76</v>
@@ -9066,7 +9073,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>74</v>
@@ -9078,15 +9085,15 @@
         <v>76</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9183,10 +9190,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9285,14 +9292,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -9314,10 +9321,10 @@
         <v>103</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N69" t="s" s="2">
         <v>106</v>
@@ -9372,7 +9379,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>74</v>
@@ -9389,10 +9396,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9415,13 +9422,13 @@
         <v>76</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9472,7 +9479,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>74</v>
@@ -9481,7 +9488,7 @@
         <v>83</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>95</v>
@@ -9489,10 +9496,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9515,13 +9522,13 @@
         <v>76</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -9572,7 +9579,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>74</v>
@@ -9581,7 +9588,7 @@
         <v>83</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>95</v>
@@ -9589,10 +9596,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9618,16 +9625,16 @@
         <v>213</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>76</v>
@@ -9655,10 +9662,10 @@
         <v>162</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>76</v>
@@ -9676,7 +9683,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>74</v>
@@ -9693,10 +9700,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9722,16 +9729,16 @@
         <v>213</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>76</v>
@@ -9759,10 +9766,10 @@
         <v>148</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>76</v>
@@ -9780,7 +9787,7 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>74</v>
@@ -9797,10 +9804,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9823,17 +9830,17 @@
         <v>76</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>76</v>
@@ -9882,7 +9889,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>74</v>
@@ -9899,10 +9906,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9928,10 +9935,10 @@
         <v>97</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9982,7 +9989,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>74</v>
@@ -9999,10 +10006,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10025,16 +10032,16 @@
         <v>84</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10084,7 +10091,7 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>74</v>
@@ -10101,10 +10108,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10127,16 +10134,16 @@
         <v>84</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10186,7 +10193,7 @@
         <v>76</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>74</v>
@@ -10203,10 +10210,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10229,19 +10236,19 @@
         <v>84</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>76</v>
@@ -10278,10 +10285,10 @@
         <v>76</v>
       </c>
       <c r="AB78" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>76</v>
@@ -10290,7 +10297,7 @@
         <v>109</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>74</v>
@@ -10307,10 +10314,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10407,10 +10414,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10509,14 +10516,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -10538,10 +10545,10 @@
         <v>103</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>106</v>
@@ -10596,7 +10603,7 @@
         <v>76</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>74</v>
@@ -10613,10 +10620,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10642,13 +10649,13 @@
         <v>213</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O82" t="s" s="2">
         <v>224</v>
@@ -10700,7 +10707,7 @@
         <v>76</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
@@ -10717,10 +10724,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10743,19 +10750,19 @@
         <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>76</v>
@@ -10804,7 +10811,7 @@
         <v>76</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>74</v>
@@ -10821,10 +10828,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10850,16 +10857,16 @@
         <v>213</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>76</v>
@@ -10887,10 +10894,10 @@
         <v>140</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>76</v>
@@ -10908,7 +10915,7 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>74</v>
@@ -10917,7 +10924,7 @@
         <v>83</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AJ84" t="s" s="2">
         <v>95</v>
@@ -10925,14 +10932,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -10954,16 +10961,16 @@
         <v>213</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>76</v>
@@ -10991,10 +10998,10 @@
         <v>140</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>76</v>
@@ -11012,7 +11019,7 @@
         <v>76</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>74</v>
@@ -11029,10 +11036,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11058,16 +11065,16 @@
         <v>77</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>76</v>
@@ -11116,7 +11123,7 @@
         <v>76</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>74</v>
@@ -11133,13 +11140,13 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>76</v>
@@ -11161,19 +11168,19 @@
         <v>84</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>76</v>
@@ -11222,7 +11229,7 @@
         <v>76</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>74</v>
@@ -11239,10 +11246,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11339,10 +11346,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11441,14 +11448,14 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11470,10 +11477,10 @@
         <v>103</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N90" t="s" s="2">
         <v>106</v>
@@ -11528,7 +11535,7 @@
         <v>76</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>74</v>
@@ -11545,10 +11552,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11574,13 +11581,13 @@
         <v>213</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>224</v>
@@ -11593,7 +11600,7 @@
         <v>76</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>76</v>
@@ -11632,7 +11639,7 @@
         <v>76</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -11649,10 +11656,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11675,19 +11682,19 @@
         <v>84</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>76</v>
@@ -11736,7 +11743,7 @@
         <v>76</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>74</v>
@@ -11753,10 +11760,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11853,10 +11860,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11955,10 +11962,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11981,19 +11988,19 @@
         <v>84</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>76</v>
@@ -12042,7 +12049,7 @@
         <v>76</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>74</v>
@@ -12059,10 +12066,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12088,20 +12095,20 @@
         <v>158</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q96" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="R96" t="s" s="2">
         <v>76</v>
@@ -12125,10 +12132,10 @@
         <v>209</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>76</v>
@@ -12146,7 +12153,7 @@
         <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>74</v>
@@ -12163,10 +12170,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12192,14 +12199,14 @@
         <v>97</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>76</v>
@@ -12209,7 +12216,7 @@
         <v>76</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>76</v>
@@ -12248,7 +12255,7 @@
         <v>76</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>74</v>
@@ -12265,10 +12272,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12294,14 +12301,14 @@
         <v>124</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>76</v>
@@ -12311,7 +12318,7 @@
         <v>76</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>76</v>
@@ -12350,7 +12357,7 @@
         <v>76</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>74</v>
@@ -12359,7 +12366,7 @@
         <v>83</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>95</v>
@@ -12367,10 +12374,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12396,16 +12403,16 @@
         <v>158</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>76</v>
@@ -12415,7 +12422,7 @@
         <v>76</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>76</v>
@@ -12454,7 +12461,7 @@
         <v>76</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>74</v>
@@ -12471,10 +12478,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12500,16 +12507,16 @@
         <v>213</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>76</v>
@@ -12537,10 +12544,10 @@
         <v>140</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>76</v>
@@ -12558,7 +12565,7 @@
         <v>76</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>74</v>
@@ -12567,7 +12574,7 @@
         <v>83</v>
       </c>
       <c r="AI100" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AJ100" t="s" s="2">
         <v>95</v>
@@ -12575,14 +12582,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -12604,16 +12611,16 @@
         <v>213</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>76</v>
@@ -12641,10 +12648,10 @@
         <v>140</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>76</v>
@@ -12662,7 +12669,7 @@
         <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>74</v>
@@ -12679,10 +12686,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12708,16 +12715,16 @@
         <v>77</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>76</v>
@@ -12766,7 +12773,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>74</v>
@@ -12783,13 +12790,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>76</v>
@@ -12811,19 +12818,19 @@
         <v>84</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>76</v>
@@ -12872,7 +12879,7 @@
         <v>76</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>74</v>
@@ -12889,10 +12896,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12989,10 +12996,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13091,14 +13098,14 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13120,10 +13127,10 @@
         <v>103</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N106" t="s" s="2">
         <v>106</v>
@@ -13178,7 +13185,7 @@
         <v>76</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>74</v>
@@ -13195,10 +13202,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13224,13 +13231,13 @@
         <v>213</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O107" t="s" s="2">
         <v>224</v>
@@ -13243,7 +13250,7 @@
         <v>76</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>76</v>
@@ -13282,7 +13289,7 @@
         <v>76</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>83</v>
@@ -13299,10 +13306,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13325,19 +13332,19 @@
         <v>84</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>76</v>
@@ -13386,7 +13393,7 @@
         <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>74</v>
@@ -13403,10 +13410,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13503,10 +13510,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13605,10 +13612,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13631,19 +13638,19 @@
         <v>84</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>76</v>
@@ -13692,7 +13699,7 @@
         <v>76</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>74</v>
@@ -13709,10 +13716,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13738,20 +13745,20 @@
         <v>158</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q112" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="R112" t="s" s="2">
         <v>76</v>
@@ -13775,10 +13782,10 @@
         <v>209</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>76</v>
@@ -13796,7 +13803,7 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>74</v>
@@ -13813,10 +13820,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13842,14 +13849,14 @@
         <v>97</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>76</v>
@@ -13859,7 +13866,7 @@
         <v>76</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>76</v>
@@ -13898,7 +13905,7 @@
         <v>76</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>74</v>
@@ -13915,10 +13922,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13944,14 +13951,14 @@
         <v>124</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>76</v>
@@ -13961,7 +13968,7 @@
         <v>76</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>76</v>
@@ -14000,7 +14007,7 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>74</v>
@@ -14009,7 +14016,7 @@
         <v>83</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>95</v>
@@ -14017,10 +14024,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14046,16 +14053,16 @@
         <v>158</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>76</v>
@@ -14065,7 +14072,7 @@
         <v>76</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>76</v>
@@ -14104,7 +14111,7 @@
         <v>76</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>74</v>
@@ -14121,10 +14128,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14150,16 +14157,16 @@
         <v>213</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>76</v>
@@ -14187,10 +14194,10 @@
         <v>140</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>76</v>
@@ -14208,7 +14215,7 @@
         <v>76</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>74</v>
@@ -14217,7 +14224,7 @@
         <v>83</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>95</v>
@@ -14225,14 +14232,14 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -14254,16 +14261,16 @@
         <v>213</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>76</v>
@@ -14291,10 +14298,10 @@
         <v>140</v>
       </c>
       <c r="Y117" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Z117" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>76</v>
@@ -14312,7 +14319,7 @@
         <v>76</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>74</v>
@@ -14329,10 +14336,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14358,16 +14365,16 @@
         <v>77</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>76</v>
@@ -14416,7 +14423,7 @@
         <v>76</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>74</v>
@@ -14433,13 +14440,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>76</v>
@@ -14461,19 +14468,19 @@
         <v>84</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>76</v>
@@ -14522,7 +14529,7 @@
         <v>76</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>74</v>
@@ -14539,10 +14546,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14639,10 +14646,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14741,14 +14748,14 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
@@ -14770,10 +14777,10 @@
         <v>103</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N122" t="s" s="2">
         <v>106</v>
@@ -14828,7 +14835,7 @@
         <v>76</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>74</v>
@@ -14845,10 +14852,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14874,13 +14881,13 @@
         <v>213</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O123" t="s" s="2">
         <v>224</v>
@@ -14893,7 +14900,7 @@
         <v>76</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>76</v>
@@ -14932,7 +14939,7 @@
         <v>76</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>83</v>
@@ -14949,10 +14956,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14975,19 +14982,19 @@
         <v>84</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O124" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>76</v>
@@ -15024,17 +15031,17 @@
         <v>76</v>
       </c>
       <c r="AB124" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AC124" s="2"/>
       <c r="AD124" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE124" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>74</v>
@@ -15051,13 +15058,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D125" t="s" s="2">
         <v>76</v>
@@ -15079,19 +15086,19 @@
         <v>84</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>76</v>
@@ -15140,7 +15147,7 @@
         <v>76</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>74</v>
@@ -15157,13 +15164,13 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>76</v>
@@ -15185,19 +15192,19 @@
         <v>84</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>76</v>
@@ -15246,7 +15253,7 @@
         <v>76</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>74</v>
@@ -15263,10 +15270,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15363,10 +15370,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15465,10 +15472,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15491,19 +15498,19 @@
         <v>84</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>76</v>
@@ -15552,7 +15559,7 @@
         <v>76</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>74</v>
@@ -15569,10 +15576,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15598,20 +15605,20 @@
         <v>158</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q130" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="R130" t="s" s="2">
         <v>76</v>
@@ -15635,10 +15642,10 @@
         <v>209</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>76</v>
@@ -15656,7 +15663,7 @@
         <v>76</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>74</v>
@@ -15673,10 +15680,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15702,14 +15709,14 @@
         <v>97</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>76</v>
@@ -15719,7 +15726,7 @@
         <v>76</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>76</v>
@@ -15758,7 +15765,7 @@
         <v>76</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>74</v>
@@ -15775,10 +15782,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15804,14 +15811,14 @@
         <v>124</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>76</v>
@@ -15821,7 +15828,7 @@
         <v>76</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>76</v>
@@ -15860,7 +15867,7 @@
         <v>76</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>74</v>
@@ -15869,7 +15876,7 @@
         <v>83</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>95</v>
@@ -15877,10 +15884,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15906,16 +15913,16 @@
         <v>158</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>76</v>
@@ -15925,7 +15932,7 @@
         <v>76</v>
       </c>
       <c r="S133" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="T133" t="s" s="2">
         <v>76</v>
@@ -15964,7 +15971,7 @@
         <v>76</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>74</v>
@@ -15981,10 +15988,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16010,16 +16017,16 @@
         <v>213</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>76</v>
@@ -16047,10 +16054,10 @@
         <v>140</v>
       </c>
       <c r="Y134" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Z134" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AA134" t="s" s="2">
         <v>76</v>
@@ -16068,7 +16075,7 @@
         <v>76</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>74</v>
@@ -16077,7 +16084,7 @@
         <v>83</v>
       </c>
       <c r="AI134" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AJ134" t="s" s="2">
         <v>95</v>
@@ -16085,14 +16092,14 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E135" s="2"/>
       <c r="F135" t="s" s="2">
@@ -16114,16 +16121,16 @@
         <v>213</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>76</v>
@@ -16151,10 +16158,10 @@
         <v>140</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>76</v>
@@ -16172,7 +16179,7 @@
         <v>76</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>74</v>
@@ -16189,10 +16196,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16218,16 +16225,16 @@
         <v>77</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>76</v>
@@ -16276,7 +16283,7 @@
         <v>76</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>74</v>
@@ -16293,13 +16300,13 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>76</v>
@@ -16321,19 +16328,19 @@
         <v>84</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>76</v>
@@ -16382,7 +16389,7 @@
         <v>76</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>74</v>
@@ -16399,10 +16406,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16499,10 +16506,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16601,14 +16608,14 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E140" s="2"/>
       <c r="F140" t="s" s="2">
@@ -16630,10 +16637,10 @@
         <v>103</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N140" t="s" s="2">
         <v>106</v>
@@ -16688,7 +16695,7 @@
         <v>76</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>74</v>
@@ -16705,10 +16712,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16734,13 +16741,13 @@
         <v>213</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="O141" t="s" s="2">
         <v>224</v>
@@ -16753,7 +16760,7 @@
         <v>76</v>
       </c>
       <c r="S141" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="T141" t="s" s="2">
         <v>76</v>
@@ -16792,7 +16799,7 @@
         <v>76</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>83</v>
@@ -16809,10 +16816,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16835,19 +16842,19 @@
         <v>84</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="O142" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="P142" t="s" s="2">
         <v>76</v>
@@ -16896,7 +16903,7 @@
         <v>76</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>74</v>
@@ -16913,10 +16920,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17013,10 +17020,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17115,10 +17122,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17141,19 +17148,19 @@
         <v>84</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>76</v>
@@ -17202,7 +17209,7 @@
         <v>76</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>74</v>
@@ -17219,10 +17226,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17248,20 +17255,20 @@
         <v>158</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q146" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="R146" t="s" s="2">
         <v>76</v>
@@ -17285,10 +17292,10 @@
         <v>209</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>76</v>
@@ -17306,7 +17313,7 @@
         <v>76</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>74</v>
@@ -17323,10 +17330,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17352,14 +17359,14 @@
         <v>97</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>76</v>
@@ -17369,7 +17376,7 @@
         <v>76</v>
       </c>
       <c r="S147" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="T147" t="s" s="2">
         <v>76</v>
@@ -17408,7 +17415,7 @@
         <v>76</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>74</v>
@@ -17425,10 +17432,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17454,14 +17461,14 @@
         <v>124</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>76</v>
@@ -17471,7 +17478,7 @@
         <v>76</v>
       </c>
       <c r="S148" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="T148" t="s" s="2">
         <v>76</v>
@@ -17510,7 +17517,7 @@
         <v>76</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>74</v>
@@ -17519,7 +17526,7 @@
         <v>83</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>95</v>
@@ -17527,10 +17534,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17556,16 +17563,16 @@
         <v>158</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>76</v>
@@ -17575,7 +17582,7 @@
         <v>76</v>
       </c>
       <c r="S149" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="T149" t="s" s="2">
         <v>76</v>
@@ -17614,7 +17621,7 @@
         <v>76</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>74</v>
@@ -17631,10 +17638,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17660,16 +17667,16 @@
         <v>213</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="O150" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P150" t="s" s="2">
         <v>76</v>
@@ -17697,10 +17704,10 @@
         <v>140</v>
       </c>
       <c r="Y150" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Z150" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>76</v>
@@ -17718,7 +17725,7 @@
         <v>76</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>74</v>
@@ -17727,7 +17734,7 @@
         <v>83</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>95</v>
@@ -17735,14 +17742,14 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -17764,16 +17771,16 @@
         <v>213</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>76</v>
@@ -17801,10 +17808,10 @@
         <v>140</v>
       </c>
       <c r="Y151" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="Z151" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AA151" t="s" s="2">
         <v>76</v>
@@ -17822,7 +17829,7 @@
         <v>76</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>74</v>
@@ -17839,10 +17846,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17868,16 +17875,16 @@
         <v>77</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N152" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>76</v>
@@ -17926,7 +17933,7 @@
         <v>76</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>74</v>

--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-observation-rauchen.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-observation-rauchen.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-30T07:50:37+00:00</t>
+    <t>2026-10-30T09:25:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-observation-rauchen.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-observation-rauchen.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4965" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4965" uniqueCount="613">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-30T09:25:40+00:00</t>
+    <t>2026-10-30T10:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1525,6 +1525,9 @@
 </t>
   </si>
   <si>
+    <t>Slicing nach component.code</t>
+  </si>
+  <si>
     <t>Observation.component.id</t>
   </si>
   <si>
@@ -1588,6 +1591,9 @@
   </si>
   <si>
     <t>packungsjahre</t>
+  </si>
+  <si>
+    <t>Packungsjahre (Packungsgröße: 20)</t>
   </si>
   <si>
     <t>Die Zahl der täglich konsumierten Zigarettenpackungen (Inhalt 20 Stück) wird mit der Zahl der Raucherjahre multipliziert (siehe https://cde.nlm.nih.gov/deView?tinyId=Q1fNmemkyg).</t>
@@ -1766,7 +1772,7 @@
     <t>zigarettenProTag</t>
   </si>
   <si>
-    <t>Component results</t>
+    <t>Anzahl täglich gerauchter Zigaretten (Teilangabe zur Berechnung der Packungsjahre)</t>
   </si>
   <si>
     <t>Observation.component:zigarettenProTag.id</t>
@@ -1831,6 +1837,9 @@
     <t>rauchbeginn</t>
   </si>
   <si>
+    <t>Rauchbeginn entweder als 'Alter bei Rauchbeginn' (Quantity in Jahren(a)) oder 'Datum bei Rauchbeginn' (dateTime)</t>
+  </si>
+  <si>
     <t>Observation.component:rauchbeginn.id</t>
   </si>
   <si>
@@ -1907,6 +1916,9 @@
   </si>
   <si>
     <t>rauchdauer</t>
+  </si>
+  <si>
+    <t>Gesamtdauer des Rauchens in Jahren (a)</t>
   </si>
   <si>
     <t>Observation.component:rauchdauer.id</t>
@@ -10288,7 +10300,7 @@
         <v>471</v>
       </c>
       <c r="AC78" t="s" s="2">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="AD78" t="s" s="2">
         <v>76</v>
@@ -10314,10 +10326,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10414,10 +10426,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10516,10 +10528,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -10620,10 +10632,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10649,13 +10661,13 @@
         <v>213</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O82" t="s" s="2">
         <v>224</v>
@@ -10707,7 +10719,7 @@
         <v>76</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
@@ -10724,10 +10736,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -10750,16 +10762,16 @@
         <v>84</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M83" t="s" s="2">
         <v>352</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O83" t="s" s="2">
         <v>354</v>
@@ -10811,7 +10823,7 @@
         <v>76</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>74</v>
@@ -10828,10 +10840,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10857,13 +10869,13 @@
         <v>213</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O84" t="s" s="2">
         <v>371</v>
@@ -10915,7 +10927,7 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>74</v>
@@ -10932,10 +10944,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11019,7 +11031,7 @@
         <v>76</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>74</v>
@@ -11036,10 +11048,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11065,10 +11077,10 @@
         <v>77</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>416</v>
@@ -11123,7 +11135,7 @@
         <v>76</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>74</v>
@@ -11140,13 +11152,13 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B87" t="s" s="2">
         <v>466</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>76</v>
@@ -11171,10 +11183,10 @@
         <v>413</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="N87" t="s" s="2">
         <v>469</v>
@@ -11246,10 +11258,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11346,10 +11358,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11448,10 +11460,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -11552,10 +11564,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -11581,13 +11593,13 @@
         <v>213</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>224</v>
@@ -11600,7 +11612,7 @@
         <v>76</v>
       </c>
       <c r="S91" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="T91" t="s" s="2">
         <v>76</v>
@@ -11639,7 +11651,7 @@
         <v>76</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -11656,10 +11668,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11682,16 +11694,16 @@
         <v>84</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M92" t="s" s="2">
         <v>352</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O92" t="s" s="2">
         <v>354</v>
@@ -11743,7 +11755,7 @@
         <v>76</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>74</v>
@@ -11760,10 +11772,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11860,10 +11872,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -11962,10 +11974,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -11988,19 +12000,19 @@
         <v>84</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>76</v>
@@ -12049,7 +12061,7 @@
         <v>76</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>74</v>
@@ -12066,10 +12078,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12095,20 +12107,20 @@
         <v>158</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q96" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="R96" t="s" s="2">
         <v>76</v>
@@ -12132,10 +12144,10 @@
         <v>209</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>76</v>
@@ -12153,7 +12165,7 @@
         <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>74</v>
@@ -12170,10 +12182,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12199,14 +12211,14 @@
         <v>97</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>76</v>
@@ -12216,7 +12228,7 @@
         <v>76</v>
       </c>
       <c r="S97" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="T97" t="s" s="2">
         <v>76</v>
@@ -12255,7 +12267,7 @@
         <v>76</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>74</v>
@@ -12272,10 +12284,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12301,14 +12313,14 @@
         <v>124</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>76</v>
@@ -12318,7 +12330,7 @@
         <v>76</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>76</v>
@@ -12357,7 +12369,7 @@
         <v>76</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>74</v>
@@ -12366,7 +12378,7 @@
         <v>83</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>95</v>
@@ -12374,10 +12386,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12403,16 +12415,16 @@
         <v>158</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>76</v>
@@ -12422,7 +12434,7 @@
         <v>76</v>
       </c>
       <c r="S99" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="T99" t="s" s="2">
         <v>76</v>
@@ -12461,7 +12473,7 @@
         <v>76</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>74</v>
@@ -12478,10 +12490,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12507,13 +12519,13 @@
         <v>213</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O100" t="s" s="2">
         <v>371</v>
@@ -12565,7 +12577,7 @@
         <v>76</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>74</v>
@@ -12582,10 +12594,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12669,7 +12681,7 @@
         <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>74</v>
@@ -12686,10 +12698,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12715,10 +12727,10 @@
         <v>77</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>416</v>
@@ -12773,7 +12785,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>74</v>
@@ -12790,13 +12802,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B103" t="s" s="2">
         <v>466</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>76</v>
@@ -12821,7 +12833,7 @@
         <v>413</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M103" t="s" s="2">
         <v>468</v>
@@ -12896,10 +12908,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -12996,10 +13008,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13098,10 +13110,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13202,10 +13214,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13231,13 +13243,13 @@
         <v>213</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O107" t="s" s="2">
         <v>224</v>
@@ -13250,7 +13262,7 @@
         <v>76</v>
       </c>
       <c r="S107" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="T107" t="s" s="2">
         <v>76</v>
@@ -13289,7 +13301,7 @@
         <v>76</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>83</v>
@@ -13306,10 +13318,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13332,16 +13344,16 @@
         <v>84</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>352</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O108" t="s" s="2">
         <v>354</v>
@@ -13393,7 +13405,7 @@
         <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>74</v>
@@ -13410,10 +13422,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13510,10 +13522,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13612,10 +13624,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13638,19 +13650,19 @@
         <v>84</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>76</v>
@@ -13699,7 +13711,7 @@
         <v>76</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>74</v>
@@ -13716,10 +13728,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13745,20 +13757,20 @@
         <v>158</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q112" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="R112" t="s" s="2">
         <v>76</v>
@@ -13782,10 +13794,10 @@
         <v>209</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>76</v>
@@ -13803,7 +13815,7 @@
         <v>76</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>74</v>
@@ -13820,10 +13832,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13849,14 +13861,14 @@
         <v>97</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>76</v>
@@ -13866,7 +13878,7 @@
         <v>76</v>
       </c>
       <c r="S113" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="T113" t="s" s="2">
         <v>76</v>
@@ -13905,7 +13917,7 @@
         <v>76</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>74</v>
@@ -13922,10 +13934,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -13951,14 +13963,14 @@
         <v>124</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>76</v>
@@ -13968,7 +13980,7 @@
         <v>76</v>
       </c>
       <c r="S114" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="T114" t="s" s="2">
         <v>76</v>
@@ -14007,7 +14019,7 @@
         <v>76</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>74</v>
@@ -14016,7 +14028,7 @@
         <v>83</v>
       </c>
       <c r="AI114" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AJ114" t="s" s="2">
         <v>95</v>
@@ -14024,10 +14036,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14053,16 +14065,16 @@
         <v>158</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O115" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>76</v>
@@ -14072,7 +14084,7 @@
         <v>76</v>
       </c>
       <c r="S115" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="T115" t="s" s="2">
         <v>76</v>
@@ -14111,7 +14123,7 @@
         <v>76</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>74</v>
@@ -14128,10 +14140,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -14157,13 +14169,13 @@
         <v>213</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O116" t="s" s="2">
         <v>371</v>
@@ -14215,7 +14227,7 @@
         <v>76</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>74</v>
@@ -14232,10 +14244,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -14319,7 +14331,7 @@
         <v>76</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>74</v>
@@ -14336,10 +14348,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -14365,10 +14377,10 @@
         <v>77</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N118" t="s" s="2">
         <v>416</v>
@@ -14423,7 +14435,7 @@
         <v>76</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>74</v>
@@ -14440,13 +14452,13 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B119" t="s" s="2">
         <v>466</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>76</v>
@@ -14471,7 +14483,7 @@
         <v>413</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>549</v>
+        <v>571</v>
       </c>
       <c r="M119" t="s" s="2">
         <v>468</v>
@@ -14546,10 +14558,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -14646,10 +14658,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -14748,10 +14760,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14852,10 +14864,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -14881,13 +14893,13 @@
         <v>213</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N123" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O123" t="s" s="2">
         <v>224</v>
@@ -14900,7 +14912,7 @@
         <v>76</v>
       </c>
       <c r="S123" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="T123" t="s" s="2">
         <v>76</v>
@@ -14939,7 +14951,7 @@
         <v>76</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>83</v>
@@ -14956,10 +14968,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -14982,16 +14994,16 @@
         <v>84</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M124" t="s" s="2">
         <v>352</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O124" t="s" s="2">
         <v>354</v>
@@ -15041,7 +15053,7 @@
         <v>356</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>74</v>
@@ -15058,10 +15070,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C125" t="s" s="2">
         <v>359</v>
@@ -15089,13 +15101,13 @@
         <v>360</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M125" t="s" s="2">
         <v>352</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O125" t="s" s="2">
         <v>354</v>
@@ -15147,7 +15159,7 @@
         <v>76</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>74</v>
@@ -15164,13 +15176,13 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D126" t="s" s="2">
         <v>76</v>
@@ -15192,16 +15204,16 @@
         <v>84</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M126" t="s" s="2">
         <v>352</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O126" t="s" s="2">
         <v>354</v>
@@ -15253,7 +15265,7 @@
         <v>76</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>74</v>
@@ -15270,10 +15282,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -15370,10 +15382,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -15472,10 +15484,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -15498,19 +15510,19 @@
         <v>84</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>76</v>
@@ -15559,7 +15571,7 @@
         <v>76</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>74</v>
@@ -15576,10 +15588,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -15605,20 +15617,20 @@
         <v>158</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q130" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="R130" t="s" s="2">
         <v>76</v>
@@ -15642,10 +15654,10 @@
         <v>209</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>76</v>
@@ -15663,7 +15675,7 @@
         <v>76</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>74</v>
@@ -15680,10 +15692,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -15709,14 +15721,14 @@
         <v>97</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>76</v>
@@ -15726,7 +15738,7 @@
         <v>76</v>
       </c>
       <c r="S131" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="T131" t="s" s="2">
         <v>76</v>
@@ -15765,7 +15777,7 @@
         <v>76</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>74</v>
@@ -15782,10 +15794,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -15811,14 +15823,14 @@
         <v>124</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>76</v>
@@ -15828,7 +15840,7 @@
         <v>76</v>
       </c>
       <c r="S132" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="T132" t="s" s="2">
         <v>76</v>
@@ -15867,7 +15879,7 @@
         <v>76</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>74</v>
@@ -15876,7 +15888,7 @@
         <v>83</v>
       </c>
       <c r="AI132" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AJ132" t="s" s="2">
         <v>95</v>
@@ -15884,10 +15896,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -15913,16 +15925,16 @@
         <v>158</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>76</v>
@@ -15932,7 +15944,7 @@
         <v>76</v>
       </c>
       <c r="S133" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="T133" t="s" s="2">
         <v>76</v>
@@ -15971,7 +15983,7 @@
         <v>76</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>74</v>
@@ -15988,10 +16000,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -16017,13 +16029,13 @@
         <v>213</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O134" t="s" s="2">
         <v>371</v>
@@ -16075,7 +16087,7 @@
         <v>76</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>74</v>
@@ -16092,10 +16104,10 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -16179,7 +16191,7 @@
         <v>76</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>74</v>
@@ -16196,10 +16208,10 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -16225,10 +16237,10 @@
         <v>77</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N136" t="s" s="2">
         <v>416</v>
@@ -16283,7 +16295,7 @@
         <v>76</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>74</v>
@@ -16300,13 +16312,13 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="B137" t="s" s="2">
         <v>466</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D137" t="s" s="2">
         <v>76</v>
@@ -16331,7 +16343,7 @@
         <v>413</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>549</v>
+        <v>596</v>
       </c>
       <c r="M137" t="s" s="2">
         <v>468</v>
@@ -16406,10 +16418,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -16506,10 +16518,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -16608,10 +16620,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -16712,10 +16724,10 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -16741,13 +16753,13 @@
         <v>213</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O141" t="s" s="2">
         <v>224</v>
@@ -16760,7 +16772,7 @@
         <v>76</v>
       </c>
       <c r="S141" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="T141" t="s" s="2">
         <v>76</v>
@@ -16799,7 +16811,7 @@
         <v>76</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>83</v>
@@ -16816,10 +16828,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -16842,16 +16854,16 @@
         <v>84</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="M142" t="s" s="2">
         <v>352</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O142" t="s" s="2">
         <v>354</v>
@@ -16903,7 +16915,7 @@
         <v>76</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>74</v>
@@ -16920,10 +16932,10 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -17020,10 +17032,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -17122,10 +17134,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -17148,19 +17160,19 @@
         <v>84</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>76</v>
@@ -17209,7 +17221,7 @@
         <v>76</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>74</v>
@@ -17226,10 +17238,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -17255,20 +17267,20 @@
         <v>158</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q146" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="R146" t="s" s="2">
         <v>76</v>
@@ -17292,10 +17304,10 @@
         <v>209</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>76</v>
@@ -17313,7 +17325,7 @@
         <v>76</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>74</v>
@@ -17330,10 +17342,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -17359,14 +17371,14 @@
         <v>97</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>76</v>
@@ -17376,7 +17388,7 @@
         <v>76</v>
       </c>
       <c r="S147" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="T147" t="s" s="2">
         <v>76</v>
@@ -17415,7 +17427,7 @@
         <v>76</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>74</v>
@@ -17432,10 +17444,10 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -17461,14 +17473,14 @@
         <v>124</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>76</v>
@@ -17478,7 +17490,7 @@
         <v>76</v>
       </c>
       <c r="S148" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="T148" t="s" s="2">
         <v>76</v>
@@ -17517,7 +17529,7 @@
         <v>76</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>74</v>
@@ -17526,7 +17538,7 @@
         <v>83</v>
       </c>
       <c r="AI148" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AJ148" t="s" s="2">
         <v>95</v>
@@ -17534,10 +17546,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17563,16 +17575,16 @@
         <v>158</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N149" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O149" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="P149" t="s" s="2">
         <v>76</v>
@@ -17582,7 +17594,7 @@
         <v>76</v>
       </c>
       <c r="S149" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="T149" t="s" s="2">
         <v>76</v>
@@ -17621,7 +17633,7 @@
         <v>76</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>74</v>
@@ -17638,10 +17650,10 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -17667,13 +17679,13 @@
         <v>213</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O150" t="s" s="2">
         <v>371</v>
@@ -17725,7 +17737,7 @@
         <v>76</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>74</v>
@@ -17742,10 +17754,10 @@
     </row>
     <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -17829,7 +17841,7 @@
         <v>76</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>74</v>
@@ -17846,10 +17858,10 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -17875,10 +17887,10 @@
         <v>77</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N152" t="s" s="2">
         <v>416</v>
@@ -17933,7 +17945,7 @@
         <v>76</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>74</v>

--- a/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-observation-rauchen.xlsx
+++ b/branches/ci/gh-pages-preview/StructureDefinition-mii-pr-kardio-observation-rauchen.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-30T10:55:39+00:00</t>
+    <t>2026-10-30T14:26:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
